--- a/project/templates/INDIA_template.xlsx
+++ b/project/templates/INDIA_template.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CUSTOM  INVOICE" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="CUSTOM  INVOICE" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="___UTC2" hidden="1">#REF!</definedName>
@@ -25,6 +25,8 @@
     <definedName name="EGMCL" hidden="1">#REF!</definedName>
     <definedName name="PGCL" hidden="1">#REF!</definedName>
     <definedName name="UTC" hidden="1">#REF!</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'CUSTOM  INVOICE'!$30:$30</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'CUSTOM  INVOICE'!$A$1:$I$49</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -32,14 +34,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="[$USD]\ #,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00_);\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.000_);\(&quot;$&quot;#,##0.000\)"/>
     <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.0000_);\(&quot;$&quot;#,##0.0000\)"/>
+    <numFmt numFmtId="169" formatCode="dd-mmm-yyyy"/>
+    <numFmt numFmtId="170" formatCode="0.00############"/>
+    <numFmt numFmtId="171" formatCode="#,##0.####"/>
+    <numFmt numFmtId="172" formatCode="&quot;USD &quot;#,##0.00"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="31">
     <font>
       <name val="Arial"/>
       <family val="2"/>
@@ -151,8 +157,68 @@
       <color theme="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00FF0000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FF0000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="000000FF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -165,8 +231,13 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9EDF2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="27">
     <border>
       <left/>
       <right/>
@@ -185,11 +256,246 @@
       </bottom>
       <diagonal/>
     </border>
+    <border/>
+    <border>
+      <top style="thin">
+        <color rgb="00777777"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00777777"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00777777"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00777777"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00777777"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <right/>
+      <top style="thin">
+        <color rgb="00777777"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00777777"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB8C2CC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB8C2CC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB8C2CC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB8C2CC"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB8C2CC"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFB8C2CC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB8C2CC"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFB8C2CC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB8C2CC"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFB8C2CC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB8C2CC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB8C2CC"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB8C2CC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB8C2CC"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB8C2CC"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFB8C2CC"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB8C2CC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB8C2CC"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFB8C2CC"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB8C2CC"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFB8C2CC"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFB8C2CC"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFB8C2CC"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFB8C2CC"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFB8C2CC"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFB8C2CC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFB8C2CC"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFB8C2CC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFB8C2CC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFB8C2CC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB8C2CC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFB8C2CC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB8C2CC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB8C2CC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFB8C2CC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB8C2CC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <right/>
+      <bottom/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="116">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -308,6 +614,176 @@
     <xf numFmtId="168" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="26" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="170" fontId="24" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="19" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="19" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="19" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="19" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="19" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="19" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="25" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="168" fontId="19" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="26" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="24" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="19" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="19" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="25" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="19" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="19" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="19" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -683,546 +1159,635 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:M49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
   <cols>
-    <col width="12.5703125" customWidth="1" min="1" max="1"/>
-    <col width="10.85546875" customWidth="1" min="2" max="2"/>
-    <col width="12.28515625" customWidth="1" min="3" max="3"/>
-    <col width="13.5703125" customWidth="1" min="4" max="4"/>
-    <col width="10.140625" customWidth="1" min="5" max="5"/>
-    <col width="8.140625" customWidth="1" min="6" max="6"/>
-    <col width="9.5703125" customWidth="1" min="7" max="7"/>
-    <col width="5.7109375" customWidth="1" min="8" max="8"/>
-    <col width="11.140625" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
     <col width="4.5703125" customWidth="1" min="10" max="10"/>
     <col width="6.5703125" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26.25" customFormat="1" customHeight="1" s="1">
-      <c r="E1" s="2" t="inlineStr">
+    <row r="1" ht="27" customFormat="1" customHeight="1" s="1">
+      <c r="A1" s="56" t="inlineStr">
         <is>
           <t>ALPHA START LIMITED</t>
         </is>
       </c>
-      <c r="F1" s="2" t="n"/>
-    </row>
-    <row r="2" ht="12.75" customFormat="1" customHeight="1" s="3">
-      <c r="E2" s="4" t="inlineStr">
+    </row>
+    <row r="2" ht="15" customFormat="1" customHeight="1" s="3">
+      <c r="A2" s="57" t="inlineStr">
         <is>
           <t>7/F, EGL TOWER</t>
         </is>
       </c>
-      <c r="F2" s="4" t="n"/>
-    </row>
-    <row r="3" ht="12.75" customFormat="1" customHeight="1" s="3">
-      <c r="E3" s="4" t="inlineStr">
+    </row>
+    <row r="3" ht="15" customFormat="1" customHeight="1" s="3">
+      <c r="A3" s="57" t="inlineStr">
         <is>
           <t>83 HUNG TO ROAD, KWUN TONG</t>
         </is>
       </c>
-      <c r="F3" s="4" t="n"/>
-    </row>
-    <row r="4" ht="12.75" customFormat="1" customHeight="1" s="3">
-      <c r="E4" s="4" t="inlineStr">
+    </row>
+    <row r="4" ht="15" customFormat="1" customHeight="1" s="3">
+      <c r="A4" s="57" t="inlineStr">
         <is>
           <t>KOWLOON, HONG KONG.</t>
         </is>
       </c>
-      <c r="F4" s="4" t="n"/>
-    </row>
-    <row r="5" ht="12.75" customFormat="1" customHeight="1" s="3">
-      <c r="E5" s="4" t="inlineStr">
+    </row>
+    <row r="5" ht="15" customFormat="1" customHeight="1" s="3">
+      <c r="A5" s="57" t="inlineStr">
         <is>
           <t>TEL: 3512 0800    FAX: 2345 8558</t>
         </is>
       </c>
-      <c r="F5" s="4" t="n"/>
-    </row>
-    <row r="6" ht="12.75" customFormat="1" customHeight="1" s="3">
-      <c r="E6" s="4" t="n"/>
-      <c r="F6" s="4" t="n"/>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="E7" s="5" t="inlineStr">
+    </row>
+    <row r="6" ht="5" customFormat="1" customHeight="1" s="3">
+      <c r="A6" s="58" t="n"/>
+      <c r="B6" s="58" t="n"/>
+      <c r="C6" s="58" t="n"/>
+      <c r="D6" s="58" t="n"/>
+      <c r="E6" s="58" t="n"/>
+      <c r="F6" s="58" t="n"/>
+      <c r="G6" s="58" t="n"/>
+      <c r="H6" s="58" t="n"/>
+      <c r="I6" s="58" t="n"/>
+    </row>
+    <row r="7" ht="25" customHeight="1">
+      <c r="A7" s="59" t="inlineStr">
         <is>
           <t>CUSTOMS INVOICE &amp; PACKING LIST</t>
         </is>
       </c>
-      <c r="F7" s="5" t="n"/>
-    </row>
-    <row r="8">
-      <c r="E8" s="3" t="n"/>
-      <c r="F8" s="3" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    </row>
+    <row r="8" ht="5" customHeight="1">
+      <c r="A8" s="58" t="n"/>
+      <c r="B8" s="58" t="n"/>
+      <c r="C8" s="58" t="n"/>
+      <c r="D8" s="58" t="n"/>
+      <c r="E8" s="58" t="n"/>
+      <c r="F8" s="58" t="n"/>
+      <c r="G8" s="58" t="n"/>
+      <c r="H8" s="58" t="n"/>
+      <c r="I8" s="58" t="n"/>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="58" t="inlineStr">
         <is>
           <t>DATE OF EXPORTATION :</t>
         </is>
       </c>
-      <c r="C9" s="6" t="n"/>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="C9" s="84" t="n"/>
+      <c r="G9" s="58" t="n"/>
+      <c r="H9" s="61" t="inlineStr">
         <is>
           <t>SHIPPING MARKS :</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="I10" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
+    <row r="10" ht="5" customHeight="1">
+      <c r="A10" s="58" t="n"/>
+      <c r="B10" s="58" t="n"/>
+      <c r="C10" s="58" t="n"/>
+      <c r="D10" s="58" t="n"/>
+      <c r="E10" s="58" t="n"/>
+      <c r="F10" s="58" t="n"/>
+      <c r="G10" s="58" t="n"/>
+      <c r="H10" s="58" t="n"/>
+      <c r="I10" s="58" t="inlineStr">
+        <is>
+          <t> </t>
         </is>
       </c>
       <c r="J10" s="8" t="n"/>
       <c r="K10" s="9" t="n"/>
     </row>
-    <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="62" t="inlineStr">
         <is>
           <t>CONSIGNEE :</t>
         </is>
       </c>
-      <c r="B11" s="10" t="n"/>
-      <c r="D11" s="1" t="n"/>
-      <c r="E11" s="1" t="n"/>
-      <c r="F11" s="1" t="n"/>
-      <c r="G11" s="1" t="n"/>
-      <c r="I11" s="1" t="n"/>
+      <c r="B11" s="63" t="n"/>
+      <c r="G11" s="58" t="n"/>
+      <c r="H11" s="64" t="n"/>
       <c r="K11" s="1" t="n"/>
     </row>
-    <row r="12" ht="14.25" customHeight="1">
-      <c r="B12" s="10" t="n"/>
-      <c r="D12" s="1" t="n"/>
-      <c r="E12" s="1" t="n"/>
-      <c r="F12" s="1" t="n"/>
-      <c r="G12" s="1" t="n"/>
-      <c r="H12" s="11" t="n"/>
-      <c r="I12" s="1" t="n"/>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="58" t="n"/>
+      <c r="B12" s="58" t="n"/>
+      <c r="G12" s="58" t="n"/>
+      <c r="H12" s="64" t="n"/>
       <c r="K12" s="1" t="n"/>
     </row>
-    <row r="13" ht="14.25" customHeight="1">
-      <c r="B13" s="10" t="n"/>
-      <c r="D13" s="1" t="n"/>
-      <c r="E13" s="1" t="n"/>
-      <c r="F13" s="1" t="n"/>
-      <c r="G13" s="1" t="n"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>C/NO.</t>
-        </is>
-      </c>
-      <c r="I13" s="11" t="n"/>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="58" t="n"/>
+      <c r="B13" s="58" t="n"/>
+      <c r="G13" s="58" t="n"/>
+      <c r="H13" s="64" t="n"/>
       <c r="K13" s="1" t="n"/>
     </row>
-    <row r="14" ht="14.25" customHeight="1">
-      <c r="B14" s="10" t="n"/>
-      <c r="D14" s="1" t="n"/>
-      <c r="E14" s="1" t="n"/>
-      <c r="F14" s="1" t="n"/>
-      <c r="G14" s="1" t="n"/>
-      <c r="I14" s="1" t="n"/>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="58" t="n"/>
+      <c r="B14" s="58" t="n"/>
+      <c r="G14" s="58" t="n"/>
+      <c r="H14" s="58" t="n"/>
+      <c r="I14" s="58" t="n"/>
       <c r="K14" s="1" t="n"/>
     </row>
-    <row r="15" ht="14.25" customHeight="1">
-      <c r="B15" s="10" t="n"/>
-      <c r="C15" s="1" t="n"/>
-      <c r="I15" s="1" t="n"/>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="58" t="n"/>
+      <c r="B15" s="58" t="n"/>
+      <c r="G15" s="58" t="n"/>
+      <c r="H15" s="58" t="n"/>
+      <c r="I15" s="58" t="n"/>
       <c r="K15" s="12" t="n"/>
     </row>
-    <row r="16" ht="14.25" customHeight="1">
-      <c r="B16" s="10" t="n"/>
-      <c r="C16" s="1" t="n"/>
-      <c r="I16" s="1" t="n"/>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="58" t="n"/>
+      <c r="B16" s="58" t="n"/>
+      <c r="G16" s="58" t="n"/>
+      <c r="H16" s="58" t="n"/>
+      <c r="I16" s="58" t="n"/>
       <c r="K16" s="12" t="n"/>
     </row>
-    <row r="17">
-      <c r="I17" s="1" t="n"/>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="109" t="inlineStr">
+        <is>
+          <t>SHIPMENT FROM:          TO:           BY:</t>
+        </is>
+      </c>
       <c r="K17" s="12" t="n"/>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>SHIPMENT FROM HONG KONG TO CHENNAI BY AIR</t>
-        </is>
-      </c>
-      <c r="B18" s="13" t="n"/>
-      <c r="C18" s="14" t="n"/>
-      <c r="D18" s="15" t="n"/>
-      <c r="I18" s="11" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="B19" s="13" t="n"/>
-      <c r="C19" s="14" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="109" t="inlineStr">
+        <is>
+          <t>ON/ABT.:</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="5" customHeight="1">
+      <c r="A19" s="58" t="n"/>
+      <c r="B19" s="65" t="n"/>
+      <c r="C19" s="58" t="n"/>
+      <c r="D19" s="58" t="n"/>
+      <c r="E19" s="58" t="n"/>
+      <c r="F19" s="58" t="n"/>
+      <c r="G19" s="58" t="n"/>
+      <c r="H19" s="58" t="n"/>
+      <c r="I19" s="58" t="n"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="66" t="inlineStr">
         <is>
           <t>COUNTRY OF ULTIMATE DESTINATION :</t>
         </is>
       </c>
-      <c r="D20" s="16" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="F20" s="16" t="n"/>
-    </row>
-    <row r="21">
-      <c r="E21" s="16" t="n"/>
-      <c r="F21" s="16" t="n"/>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="17" t="n"/>
-      <c r="B22" s="18" t="n"/>
-      <c r="C22" s="18" t="n"/>
-      <c r="D22" s="18" t="n"/>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="17" t="n"/>
-      <c r="B23" s="18" t="n"/>
-      <c r="C23" s="18" t="n"/>
-      <c r="D23" s="18" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="19" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="D20" s="63" t="n"/>
+    </row>
+    <row r="21" ht="5" customHeight="1">
+      <c r="A21" s="58" t="n"/>
+      <c r="B21" s="58" t="n"/>
+      <c r="C21" s="58" t="n"/>
+      <c r="D21" s="58" t="n"/>
+      <c r="E21" s="58" t="n"/>
+      <c r="F21" s="58" t="n"/>
+      <c r="G21" s="58" t="n"/>
+      <c r="H21" s="58" t="n"/>
+      <c r="I21" s="58" t="n"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PORT OF DISCHARGE: </t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SHIPMENT TERMS: </t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="5" customHeight="1">
+      <c r="A24" s="58" t="n"/>
+      <c r="B24" s="58" t="n"/>
+      <c r="C24" s="58" t="n"/>
+      <c r="D24" s="58" t="n"/>
+      <c r="E24" s="58" t="n"/>
+      <c r="F24" s="58" t="n"/>
+      <c r="G24" s="58" t="n"/>
+      <c r="H24" s="58" t="n"/>
+      <c r="I24" s="58" t="n"/>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="58" t="inlineStr">
         <is>
           <t>CUSTOMS INVOICE NO.</t>
         </is>
       </c>
-      <c r="C25" s="16" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="C25" s="63" t="n"/>
+      <c r="G25" s="58" t="n"/>
+      <c r="H25" s="58" t="n"/>
+      <c r="I25" s="58" t="n"/>
+    </row>
+    <row r="26" ht="5" customHeight="1">
+      <c r="A26" s="58" t="n"/>
+      <c r="B26" s="58" t="n"/>
+      <c r="C26" s="58" t="n"/>
+      <c r="D26" s="58" t="n"/>
+      <c r="E26" s="58" t="n"/>
+      <c r="F26" s="58" t="n"/>
+      <c r="G26" s="58" t="n"/>
+      <c r="H26" s="58" t="n"/>
+      <c r="I26" s="58" t="n"/>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="58" t="inlineStr">
         <is>
           <t>TOTAL :</t>
         </is>
       </c>
-      <c r="B27" s="4" t="n"/>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="B27" s="67" t="n"/>
+      <c r="C27" s="58" t="inlineStr">
         <is>
           <t>PKG(S) ONLY.</t>
         </is>
       </c>
-      <c r="F27" s="20" t="inlineStr">
+      <c r="F27" s="58" t="inlineStr">
         <is>
           <t>G.W.</t>
         </is>
       </c>
-      <c r="G27" s="21" t="n"/>
-      <c r="H27" s="3" t="inlineStr">
+      <c r="G27" s="85" t="n"/>
+      <c r="H27" s="58" t="inlineStr">
         <is>
           <t>KGS</t>
         </is>
       </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="n"/>
-      <c r="B28" s="4" t="n"/>
-      <c r="C28" s="3" t="n"/>
-      <c r="F28" s="20" t="n"/>
-      <c r="G28" s="21" t="n"/>
-      <c r="H28" s="3" t="n"/>
-    </row>
-    <row r="29">
-      <c r="I29" s="22" t="n"/>
+      <c r="I27" s="58" t="n"/>
+    </row>
+    <row r="28" ht="5" customHeight="1">
+      <c r="A28" s="58" t="n"/>
+      <c r="B28" s="58" t="n"/>
+      <c r="C28" s="58" t="n"/>
+      <c r="D28" s="58" t="n"/>
+      <c r="E28" s="58" t="n"/>
+      <c r="F28" s="58" t="n"/>
+      <c r="G28" s="69" t="n"/>
+      <c r="H28" s="58" t="n"/>
+      <c r="I28" s="58" t="n"/>
+    </row>
+    <row r="29" ht="5" customHeight="1">
+      <c r="A29" s="58" t="n"/>
+      <c r="B29" s="58" t="n"/>
+      <c r="C29" s="58" t="n"/>
+      <c r="D29" s="58" t="n"/>
+      <c r="E29" s="58" t="n"/>
+      <c r="F29" s="58" t="n"/>
+      <c r="G29" s="58" t="n"/>
+      <c r="H29" s="58" t="n"/>
+      <c r="I29" s="58" t="n"/>
       <c r="J29" s="22" t="n"/>
       <c r="K29" s="22" t="n"/>
     </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr">
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="90" t="inlineStr">
         <is>
           <t>C/NO.</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B30" s="90" t="inlineStr">
         <is>
           <t>DESCRIPTION  OF  GOODS</t>
         </is>
       </c>
-      <c r="E30" s="23" t="inlineStr">
+      <c r="C30" s="111" t="n"/>
+      <c r="D30" s="112" t="n"/>
+      <c r="E30" s="90" t="inlineStr">
         <is>
           <t>HS CODE</t>
         </is>
       </c>
-      <c r="G30" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">QUANTITY </t>
-        </is>
-      </c>
-      <c r="I30" s="23" t="inlineStr">
-        <is>
-          <t>AMOUNT</t>
+      <c r="F30" s="90" t="inlineStr">
+        <is>
+          <t>QUANTITY</t>
+        </is>
+      </c>
+      <c r="G30" s="112" t="n"/>
+      <c r="H30" s="91" t="n"/>
+      <c r="I30" s="94" t="inlineStr">
+        <is>
+          <t>AMOUNT
+(USD)</t>
         </is>
       </c>
       <c r="J30" s="23" t="n"/>
       <c r="K30" s="23" t="n"/>
     </row>
-    <row r="31">
-      <c r="A31" s="7" t="n"/>
-      <c r="B31" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E31" s="22" t="n"/>
-      <c r="G31" s="24" t="n"/>
-      <c r="I31" s="23" t="n"/>
+    <row r="31" ht="3" customHeight="1">
+      <c r="A31" s="95" t="n"/>
+      <c r="B31" s="96" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="C31" s="97" t="n"/>
+      <c r="D31" s="98" t="n"/>
+      <c r="E31" s="95" t="n"/>
+      <c r="F31" s="99" t="n"/>
+      <c r="G31" s="98" t="n"/>
+      <c r="H31" s="96" t="n"/>
+      <c r="I31" s="100" t="n"/>
       <c r="J31" s="23" t="n"/>
       <c r="K31" s="23" t="n"/>
     </row>
-    <row r="32">
-      <c r="A32" s="7" t="n"/>
-      <c r="B32" s="25" t="n"/>
-      <c r="E32" s="22" t="n"/>
-      <c r="G32" s="24" t="n"/>
-      <c r="I32" s="23" t="n"/>
+    <row r="32" ht="3" customHeight="1">
+      <c r="A32" s="95" t="n"/>
+      <c r="B32" s="96" t="n"/>
+      <c r="C32" s="97" t="n"/>
+      <c r="D32" s="98" t="n"/>
+      <c r="E32" s="95" t="n"/>
+      <c r="F32" s="99" t="n"/>
+      <c r="G32" s="98" t="n"/>
+      <c r="H32" s="96" t="n"/>
+      <c r="I32" s="100" t="n"/>
       <c r="J32" s="23" t="n"/>
       <c r="K32" s="23" t="n"/>
     </row>
-    <row r="33" ht="12.75" customHeight="1">
-      <c r="A33" s="9" t="n"/>
-      <c r="B33" s="25" t="n"/>
-      <c r="C33" s="1" t="n"/>
-      <c r="D33" s="1" t="n"/>
-      <c r="E33" s="26" t="n"/>
-      <c r="F33" s="27" t="n"/>
-      <c r="I33" s="28" t="n"/>
+    <row r="33" ht="26" customHeight="1">
+      <c r="A33" s="101" t="n"/>
+      <c r="B33" s="113" t="n"/>
+      <c r="C33" s="114" t="n"/>
+      <c r="D33" s="115" t="n"/>
+      <c r="E33" s="105" t="n"/>
+      <c r="F33" s="106" t="n"/>
+      <c r="G33" s="107" t="n"/>
+      <c r="H33" s="102" t="n"/>
+      <c r="I33" s="108" t="n"/>
       <c r="J33" s="27" t="n"/>
       <c r="K33" s="29" t="n"/>
     </row>
-    <row r="34" ht="12.75" customHeight="1">
-      <c r="A34" s="9" t="n"/>
-      <c r="B34" s="25" t="n"/>
-      <c r="C34" s="1" t="n"/>
-      <c r="D34" s="1" t="n"/>
-      <c r="E34" s="26" t="n"/>
-      <c r="F34" s="27" t="n"/>
-      <c r="I34" s="28" t="n"/>
+    <row r="34" ht="26" customHeight="1">
+      <c r="A34" s="101" t="n"/>
+      <c r="B34" s="113" t="n"/>
+      <c r="C34" s="114" t="n"/>
+      <c r="D34" s="115" t="n"/>
+      <c r="E34" s="105" t="n"/>
+      <c r="F34" s="106" t="n"/>
+      <c r="G34" s="107" t="n"/>
+      <c r="H34" s="102" t="n"/>
+      <c r="I34" s="108" t="n"/>
       <c r="J34" s="27" t="n"/>
       <c r="K34" s="29" t="n"/>
     </row>
-    <row r="35" ht="12.75" customHeight="1">
-      <c r="A35" s="9" t="n"/>
-      <c r="B35" s="25" t="n"/>
-      <c r="C35" s="1" t="n"/>
-      <c r="D35" s="1" t="n"/>
-      <c r="E35" s="26" t="n"/>
-      <c r="F35" s="27" t="n"/>
-      <c r="I35" s="28" t="n"/>
+    <row r="35" ht="26" customHeight="1">
+      <c r="A35" s="101" t="n"/>
+      <c r="B35" s="113" t="n"/>
+      <c r="C35" s="114" t="n"/>
+      <c r="D35" s="115" t="n"/>
+      <c r="E35" s="105" t="n"/>
+      <c r="F35" s="106" t="n"/>
+      <c r="G35" s="107" t="n"/>
+      <c r="H35" s="102" t="n"/>
+      <c r="I35" s="108" t="n"/>
       <c r="J35" s="27" t="n"/>
       <c r="K35" s="29" t="n"/>
     </row>
-    <row r="36" ht="12.75" customHeight="1">
-      <c r="A36" s="9" t="n"/>
-      <c r="B36" s="25" t="n"/>
-      <c r="C36" s="1" t="n"/>
-      <c r="D36" s="1" t="n"/>
-      <c r="E36" s="26" t="n"/>
-      <c r="F36" s="27" t="n"/>
-      <c r="I36" s="28" t="n"/>
+    <row r="36" ht="26" customHeight="1">
+      <c r="A36" s="101" t="n"/>
+      <c r="B36" s="113" t="n"/>
+      <c r="C36" s="114" t="n"/>
+      <c r="D36" s="115" t="n"/>
+      <c r="E36" s="105" t="n"/>
+      <c r="F36" s="106" t="n"/>
+      <c r="G36" s="107" t="n"/>
+      <c r="H36" s="102" t="n"/>
+      <c r="I36" s="108" t="n"/>
       <c r="J36" s="27" t="n"/>
       <c r="K36" s="29" t="n"/>
     </row>
-    <row r="37" ht="12.75" customHeight="1">
-      <c r="A37" s="9" t="n"/>
-      <c r="B37" s="25" t="n"/>
-      <c r="C37" s="1" t="n"/>
-      <c r="D37" s="1" t="n"/>
-      <c r="E37" s="26" t="n"/>
-      <c r="F37" s="27" t="n"/>
-      <c r="I37" s="28" t="n"/>
+    <row r="37" ht="26" customHeight="1">
+      <c r="A37" s="101" t="n"/>
+      <c r="B37" s="113" t="n"/>
+      <c r="C37" s="114" t="n"/>
+      <c r="D37" s="115" t="n"/>
+      <c r="E37" s="105" t="n"/>
+      <c r="F37" s="106" t="n"/>
+      <c r="G37" s="107" t="n"/>
+      <c r="H37" s="102" t="n"/>
+      <c r="I37" s="108" t="n"/>
       <c r="J37" s="27" t="n"/>
       <c r="K37" s="29" t="n"/>
     </row>
-    <row r="38" ht="12.75" customHeight="1">
-      <c r="A38" s="9" t="n"/>
-      <c r="B38" s="25" t="n"/>
-      <c r="C38" s="1" t="n"/>
-      <c r="D38" s="1" t="n"/>
-      <c r="E38" s="26" t="n"/>
-      <c r="F38" s="27" t="n"/>
-      <c r="I38" s="28" t="n"/>
+    <row r="38" ht="26" customHeight="1">
+      <c r="A38" s="101" t="n"/>
+      <c r="B38" s="113" t="n"/>
+      <c r="C38" s="114" t="n"/>
+      <c r="D38" s="115" t="n"/>
+      <c r="E38" s="105" t="n"/>
+      <c r="F38" s="106" t="n"/>
+      <c r="G38" s="107" t="n"/>
+      <c r="H38" s="102" t="n"/>
+      <c r="I38" s="108" t="n"/>
       <c r="J38" s="27" t="n"/>
       <c r="K38" s="29" t="n"/>
     </row>
-    <row r="39" ht="12.75" customHeight="1">
-      <c r="A39" s="9" t="n"/>
-      <c r="B39" s="25" t="n"/>
-      <c r="C39" s="1" t="n"/>
-      <c r="D39" s="1" t="n"/>
-      <c r="E39" s="26" t="n"/>
-      <c r="F39" s="27" t="n"/>
-      <c r="I39" s="28" t="n"/>
+    <row r="39" ht="5" customHeight="1">
+      <c r="A39" s="75" t="n"/>
+      <c r="B39" s="58" t="n"/>
+      <c r="C39" s="58" t="n"/>
+      <c r="D39" s="58" t="n"/>
+      <c r="E39" s="58" t="n"/>
+      <c r="F39" s="76" t="n"/>
+      <c r="G39" s="58" t="n"/>
+      <c r="H39" s="58" t="n"/>
+      <c r="I39" s="77" t="n"/>
       <c r="J39" s="27" t="n"/>
       <c r="K39" s="29" t="n"/>
     </row>
-    <row r="40" ht="12.75" customHeight="1">
-      <c r="A40" s="9" t="n"/>
-      <c r="B40" s="25" t="n"/>
-      <c r="C40" s="1" t="n"/>
-      <c r="D40" s="1" t="n"/>
-      <c r="E40" s="26" t="n"/>
-      <c r="F40" s="27" t="n"/>
-      <c r="I40" s="28" t="n"/>
+    <row r="40" ht="5" customHeight="1">
+      <c r="A40" s="75" t="n"/>
+      <c r="B40" s="58" t="n"/>
+      <c r="C40" s="58" t="n"/>
+      <c r="D40" s="58" t="n"/>
+      <c r="E40" s="58" t="n"/>
+      <c r="F40" s="76" t="n"/>
+      <c r="G40" s="58" t="n"/>
+      <c r="H40" s="58" t="n"/>
+      <c r="I40" s="77" t="n"/>
       <c r="J40" s="27" t="n"/>
       <c r="K40" s="29" t="n"/>
     </row>
-    <row r="41" ht="12.75" customHeight="1">
-      <c r="A41" s="9" t="n"/>
-      <c r="B41" s="25" t="n"/>
-      <c r="C41" s="1" t="n"/>
-      <c r="D41" s="1" t="n"/>
-      <c r="E41" s="26" t="n"/>
-      <c r="F41" s="27" t="n"/>
-      <c r="I41" s="28" t="n"/>
+    <row r="41" ht="5" customHeight="1">
+      <c r="A41" s="75" t="n"/>
+      <c r="B41" s="58" t="n"/>
+      <c r="C41" s="58" t="n"/>
+      <c r="D41" s="58" t="n"/>
+      <c r="E41" s="58" t="n"/>
+      <c r="F41" s="76" t="n"/>
+      <c r="G41" s="58" t="n"/>
+      <c r="H41" s="58" t="n"/>
+      <c r="I41" s="77" t="n"/>
       <c r="J41" s="27" t="n"/>
       <c r="K41" s="29" t="n"/>
     </row>
-    <row r="42" ht="15.95" customHeight="1" thickBot="1">
-      <c r="B42" s="25" t="n"/>
-      <c r="C42" s="1" t="n"/>
-      <c r="D42" s="1" t="n"/>
-      <c r="H42" s="32" t="inlineStr">
+    <row r="42" ht="27" customHeight="1" thickBot="1">
+      <c r="A42" s="58" t="n"/>
+      <c r="B42" s="58" t="n"/>
+      <c r="C42" s="58" t="n"/>
+      <c r="D42" s="58" t="n"/>
+      <c r="E42" s="58" t="n"/>
+      <c r="F42" s="58" t="n"/>
+      <c r="G42" s="58" t="n"/>
+      <c r="H42" s="78" t="inlineStr">
         <is>
           <t>TOTAL VALUE:</t>
         </is>
       </c>
-      <c r="I42" s="33" t="n"/>
+      <c r="I42" s="89" t="n"/>
       <c r="J42" s="34" t="n"/>
       <c r="K42" s="31" t="n"/>
       <c r="L42" s="22" t="n"/>
       <c r="M42" s="22" t="n"/>
     </row>
-    <row r="43" ht="12.75" customHeight="1" thickTop="1">
-      <c r="B43" s="31" t="n"/>
-      <c r="C43" s="31" t="n"/>
-      <c r="D43" s="35" t="n"/>
-      <c r="E43" s="31" t="n"/>
-      <c r="F43" s="31" t="n"/>
-      <c r="G43" s="36" t="n"/>
-      <c r="H43" s="30" t="n"/>
-      <c r="I43" s="30" t="n"/>
+    <row r="43" ht="5" customHeight="1" thickTop="1">
+      <c r="A43" s="58" t="n"/>
+      <c r="B43" s="58" t="n"/>
+      <c r="C43" s="58" t="n"/>
+      <c r="D43" s="80" t="n"/>
+      <c r="E43" s="58" t="n"/>
+      <c r="F43" s="58" t="n"/>
+      <c r="G43" s="76" t="n"/>
+      <c r="H43" s="58" t="n"/>
+      <c r="I43" s="58" t="n"/>
       <c r="J43" s="31" t="n"/>
       <c r="K43" s="51" t="n"/>
       <c r="L43" s="22" t="n"/>
       <c r="M43" s="22" t="n"/>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>NO COMMERCIAL VALUE</t>
-        </is>
-      </c>
-      <c r="B44" s="22" t="n"/>
-      <c r="C44" s="22" t="n"/>
-      <c r="D44" s="38" t="n"/>
-      <c r="E44" s="22" t="n"/>
-      <c r="F44" s="22" t="n"/>
-      <c r="G44" s="22" t="n"/>
-      <c r="H44" s="22" t="n"/>
-      <c r="I44" s="22" t="n"/>
+    <row r="44" ht="5" customHeight="1">
+      <c r="A44" s="58" t="n"/>
+      <c r="B44" s="58" t="n"/>
+      <c r="C44" s="58" t="n"/>
+      <c r="D44" s="80" t="n"/>
+      <c r="E44" s="58" t="n"/>
+      <c r="F44" s="58" t="n"/>
+      <c r="G44" s="58" t="n"/>
+      <c r="H44" s="58" t="n"/>
+      <c r="I44" s="58" t="n"/>
       <c r="J44" s="22" t="n"/>
       <c r="K44" s="22" t="n"/>
       <c r="L44" s="22" t="n"/>
       <c r="M44" s="22" t="n"/>
     </row>
-    <row r="45">
-      <c r="A45" s="19" t="inlineStr">
-        <is>
-          <t>INVOICE ONLY FOR CUSTOMS PURPOSE</t>
-        </is>
-      </c>
-      <c r="D45" s="38" t="n"/>
-      <c r="G45" s="39" t="n"/>
-      <c r="H45" s="40" t="n"/>
-      <c r="I45" s="52" t="n"/>
+    <row r="45" ht="5" customHeight="1">
+      <c r="A45" s="58" t="n"/>
+      <c r="B45" s="58" t="n"/>
+      <c r="C45" s="58" t="n"/>
+      <c r="D45" s="80" t="n"/>
+      <c r="E45" s="58" t="n"/>
+      <c r="F45" s="58" t="n"/>
+      <c r="G45" s="58" t="n"/>
+      <c r="H45" s="58" t="n"/>
+      <c r="I45" s="81" t="n"/>
       <c r="J45" s="51" t="n"/>
       <c r="K45" s="51" t="n"/>
       <c r="L45" s="22" t="n"/>
       <c r="M45" s="22" t="n"/>
     </row>
-    <row r="46" ht="9.6" customHeight="1">
-      <c r="A46" s="32" t="n"/>
-      <c r="B46" s="42" t="n"/>
-      <c r="C46" s="43" t="n"/>
-      <c r="D46" s="16" t="n"/>
-      <c r="E46" s="43" t="n"/>
-      <c r="F46" s="43" t="n"/>
-      <c r="G46" s="16" t="n"/>
-      <c r="H46" s="1" t="n"/>
-      <c r="I46" s="53" t="n"/>
+    <row r="46" ht="5" customHeight="1">
+      <c r="A46" s="58" t="n"/>
+      <c r="B46" s="58" t="n"/>
+      <c r="C46" s="58" t="n"/>
+      <c r="D46" s="58" t="n"/>
+      <c r="E46" s="58" t="n"/>
+      <c r="F46" s="58" t="n"/>
+      <c r="G46" s="58" t="n"/>
+      <c r="H46" s="58" t="n"/>
+      <c r="I46" s="82" t="n"/>
       <c r="J46" s="54" t="n"/>
       <c r="K46" s="54" t="n"/>
     </row>
-    <row r="47" ht="15" customHeight="1">
-      <c r="A47" s="46" t="inlineStr">
-        <is>
-          <t>THIS IS TRADE SAMPLES AND NOT FOR SALE.</t>
-        </is>
-      </c>
-      <c r="B47" s="47" t="n"/>
-      <c r="C47" s="48" t="n"/>
-      <c r="D47" s="47" t="n"/>
-      <c r="E47" s="48" t="n"/>
-      <c r="F47" s="48" t="n"/>
-      <c r="G47" s="13" t="n"/>
-      <c r="H47" s="1" t="n"/>
-      <c r="I47" s="55" t="n"/>
+    <row r="47" ht="50" customHeight="1">
+      <c r="A47" s="83" t="inlineStr">
+        <is>
+          <t>THIS IS TRADE SAMPLES AND NOT FOR SALE.
+THERE IS NO COMMERCIAL VALUE AND FOREIGN EXCHANGE INVOLVED.
+VALUE DECLARED FOR CUSTOMS PURPOSE ONLY.</t>
+        </is>
+      </c>
       <c r="J47" s="54" t="n"/>
       <c r="K47" s="54" t="n"/>
     </row>
-    <row r="48" ht="15" customHeight="1">
-      <c r="A48" s="46" t="inlineStr">
-        <is>
-          <t>THERE IS NO COMMERCIAL VALUE AND FOREIGN EXCHANGE INVOLVED.</t>
-        </is>
-      </c>
-      <c r="B48" s="47" t="n"/>
-      <c r="C48" s="48" t="n"/>
-      <c r="D48" s="47" t="n"/>
-      <c r="E48" s="48" t="n"/>
-      <c r="F48" s="48" t="n"/>
-      <c r="G48" s="13" t="n"/>
-      <c r="H48" s="1" t="n"/>
-      <c r="I48" s="55" t="n"/>
+    <row r="48" ht="4" customHeight="1">
+      <c r="A48" s="83" t="n"/>
       <c r="J48" s="54" t="n"/>
       <c r="K48" s="54" t="n"/>
     </row>
-    <row r="49" ht="15" customHeight="1">
-      <c r="A49" s="46" t="inlineStr">
-        <is>
-          <t>VALUE DECLARED FOR CUSTOMS PURPOSE ONLY.</t>
-        </is>
-      </c>
-      <c r="B49" s="47" t="n"/>
-      <c r="C49" s="50" t="n"/>
-      <c r="D49" s="47" t="n"/>
-      <c r="E49" s="48" t="n"/>
-      <c r="F49" s="48" t="n"/>
-      <c r="G49" s="13" t="n"/>
-      <c r="H49" s="1" t="n"/>
-      <c r="I49" s="55" t="n"/>
+    <row r="49" ht="4" customHeight="1">
+      <c r="A49" s="83" t="n"/>
       <c r="J49" s="54" t="n"/>
       <c r="K49" s="54" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="38">
+    <mergeCell ref="A7:I7"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="A18:I18"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="A47:I47"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="A23:I23"/>
+    <mergeCell ref="A17:I17"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="A22:I22"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="D20:I20"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="A48:I48"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="A49:I49"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A9:B9"/>
+  </mergeCells>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.35" right="0" top="0.7" bottom="0.5" header="0.37" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9" blackAndWhite="1"/>
+  <pageMargins left="0.35" right="0.35" top="0.65" bottom="0.55" header="0.2" footer="0.2"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1" blackAndWhite="0"/>
   <headerFooter alignWithMargins="0">
     <oddHeader>&amp;L_x000a_</oddHeader>
-    <oddFooter>&amp;L&amp;F&amp;CP.&amp;P/&amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;F</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
